--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/15gps/3mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/15gps/3mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X39"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.54993157407</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>496.4483338764089</v>
       </c>
-      <c r="W2" t="b">
+      <c r="V2" t="b">
         <v>0</v>
       </c>
+      <c r="W2" t="s">
+        <v>29</v>
+      </c>
       <c r="X2">
-        <v>503.1047816204058</v>
+        <v>0.246256452</v>
+      </c>
+      <c r="Y2">
+        <v>0.261310946</v>
+      </c>
+      <c r="Z2">
+        <v>0.3590621821510074</v>
+      </c>
+      <c r="AA2">
+        <v>7.527247000000003</v>
+      </c>
+      <c r="AB2">
+        <v>0.04873857230565529</v>
+      </c>
+      <c r="AC2">
+        <v>24.19618301665745</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.55004731481</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>498.0396229993363</v>
       </c>
-      <c r="W3" t="b">
+      <c r="V3" t="b">
         <v>0</v>
       </c>
+      <c r="W3">
+        <v>502.7327294678793</v>
+      </c>
+      <c r="X3">
+        <v>0.246228826</v>
+      </c>
+      <c r="Y3">
+        <v>0.261290576</v>
+      </c>
+      <c r="Z3">
+        <v>0.3590284109367252</v>
+      </c>
+      <c r="AA3">
+        <v>7.530875000000002</v>
+      </c>
+      <c r="AB3">
+        <v>0.0487116922920822</v>
+      </c>
+      <c r="AC3">
+        <v>24.26035286480829</v>
+      </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.55016305556</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>496.8866113664767</v>
       </c>
-      <c r="V4">
-        <v>0.8219614809057519</v>
-      </c>
-      <c r="W4" t="b">
-        <v>1</v>
+      <c r="V4" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.246211996</v>
+      </c>
+      <c r="Y4">
+        <v>0.261285166</v>
+      </c>
+      <c r="Z4">
+        <v>0.3590129314466981</v>
+      </c>
+      <c r="AA4">
+        <v>7.536585000000002</v>
+      </c>
+      <c r="AB4">
+        <v>0.04867433229765029</v>
+      </c>
+      <c r="AC4">
+        <v>24.1856240359053</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.550279375</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>497.1036161096673</v>
       </c>
-      <c r="V5">
-        <v>0.6127310151532759</v>
-      </c>
-      <c r="W5" t="b">
-        <v>1</v>
+      <c r="V5" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>24.24868057004817</v>
+      </c>
+      <c r="X5">
+        <v>0.246178652</v>
+      </c>
+      <c r="Y5">
+        <v>0.26127339</v>
+      </c>
+      <c r="Z5">
+        <v>0.3589814939835049</v>
+      </c>
+      <c r="AA5">
+        <v>7.547369000000003</v>
+      </c>
+      <c r="AB5">
+        <v>0.04860364563398225</v>
+      </c>
+      <c r="AC5">
+        <v>24.16104800076542</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.55039569444</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>497.9913179606584</v>
       </c>
-      <c r="V6">
-        <v>0.5853036667759998</v>
-      </c>
-      <c r="W6" t="b">
-        <v>1</v>
+      <c r="V6" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0.246156742</v>
+      </c>
+      <c r="Y6">
+        <v>0.261265432</v>
+      </c>
+      <c r="Z6">
+        <v>0.3589606769413625</v>
+      </c>
+      <c r="AA6">
+        <v>7.554345000000005</v>
+      </c>
+      <c r="AB6">
+        <v>0.04855796719388808</v>
+      </c>
+      <c r="AC6">
+        <v>24.18144608037474</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.55051143518</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>498.8268206217696</v>
       </c>
-      <c r="V7">
-        <v>0.8617340138258576</v>
-      </c>
-      <c r="W7" t="b">
-        <v>1</v>
+      <c r="V7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0.24610657</v>
+      </c>
+      <c r="Y7">
+        <v>0.261260022</v>
+      </c>
+      <c r="Z7">
+        <v>0.3589223354607586</v>
+      </c>
+      <c r="AA7">
+        <v>7.576726000000001</v>
+      </c>
+      <c r="AB7">
+        <v>0.04841567169543535</v>
+      </c>
+      <c r="AC7">
+        <v>24.15103558010141</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.55062775463</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>497.5800422248978</v>
       </c>
-      <c r="V8">
-        <v>0.6353042313799542</v>
-      </c>
-      <c r="W8" t="b">
-        <v>1</v>
+      <c r="V8" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0.246097678</v>
+      </c>
+      <c r="Y8">
+        <v>0.261236788</v>
+      </c>
+      <c r="Z8">
+        <v>0.3588993264434313</v>
+      </c>
+      <c r="AA8">
+        <v>7.569555000000001</v>
+      </c>
+      <c r="AB8">
+        <v>0.048456608106704</v>
+      </c>
+      <c r="AC8">
+        <v>24.1110411078091</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.55074349537</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>499.5688896971513</v>
       </c>
-      <c r="V9">
-        <v>1.005040393171076</v>
-      </c>
-      <c r="W9" t="b">
-        <v>1</v>
+      <c r="V9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0.246062748</v>
+      </c>
+      <c r="Y9">
+        <v>0.261221828</v>
+      </c>
+      <c r="Z9">
+        <v>0.3588644860904643</v>
+      </c>
+      <c r="AA9">
+        <v>7.579540000000001</v>
+      </c>
+      <c r="AB9">
+        <v>0.04839099613708542</v>
+      </c>
+      <c r="AC9">
+        <v>24.1746362115429</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.55085981482</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>501.1320380382691</v>
       </c>
-      <c r="V10">
-        <v>1.780244424343363</v>
-      </c>
-      <c r="W10" t="b">
+      <c r="V10" t="b">
         <v>1</v>
       </c>
+      <c r="X10">
+        <v>0.246057032</v>
+      </c>
+      <c r="Y10">
+        <v>0.261217054</v>
+      </c>
+      <c r="Z10">
+        <v>0.3588570917469626</v>
+      </c>
+      <c r="AA10">
+        <v>7.580010999999999</v>
+      </c>
+      <c r="AB10">
+        <v>0.04838716322413161</v>
+      </c>
+      <c r="AC10">
+        <v>24.24835772139945</v>
+      </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.55097555555</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>502.2273854963766</v>
       </c>
-      <c r="V11">
-        <v>1.336089986042359</v>
-      </c>
-      <c r="W11" t="b">
+      <c r="V11" t="b">
         <v>1</v>
       </c>
+      <c r="X11">
+        <v>0.246014482</v>
+      </c>
+      <c r="Y11">
+        <v>0.26120146</v>
+      </c>
+      <c r="Z11">
+        <v>0.358816566033203</v>
+      </c>
+      <c r="AA11">
+        <v>7.593488999999998</v>
+      </c>
+      <c r="AB11">
+        <v>0.04829972888400066</v>
+      </c>
+      <c r="AC11">
+        <v>24.25744655759548</v>
+      </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.551091875</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>504.1845904872516</v>
       </c>
-      <c r="V12">
-        <v>1.546421346424898</v>
-      </c>
-      <c r="W12" t="b">
+      <c r="V12" t="b">
         <v>1</v>
       </c>
+      <c r="X12">
+        <v>0.245997652</v>
+      </c>
+      <c r="Y12">
+        <v>0.261199232</v>
+      </c>
+      <c r="Z12">
+        <v>0.358803405205278</v>
+      </c>
+      <c r="AA12">
+        <v>7.600789999999996</v>
+      </c>
+      <c r="AB12">
+        <v>0.0482536299309204</v>
+      </c>
+      <c r="AC12">
+        <v>24.32873664624449</v>
+      </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.55120761574</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>502.3546093965629</v>
       </c>
-      <c r="V13">
-        <v>1.095115525820271</v>
-      </c>
-      <c r="W13" t="b">
+      <c r="V13" t="b">
         <v>1</v>
       </c>
+      <c r="X13">
+        <v>0.245982092</v>
+      </c>
+      <c r="Y13">
+        <v>0.26119764</v>
+      </c>
+      <c r="Z13">
+        <v>0.3587915783937327</v>
+      </c>
+      <c r="AA13">
+        <v>7.607774000000006</v>
+      </c>
+      <c r="AB13">
+        <v>0.04820971523819206</v>
+      </c>
+      <c r="AC13">
+        <v>24.2183726676015</v>
+      </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.55132335648</v>
       </c>
@@ -1411,14 +1642,29 @@
       <c r="U14">
         <v>502.3038250994525</v>
       </c>
-      <c r="V14">
-        <v>1.07150114955973</v>
-      </c>
-      <c r="W14" t="b">
+      <c r="V14" t="b">
         <v>1</v>
       </c>
+      <c r="X14">
+        <v>0.245981458</v>
+      </c>
+      <c r="Y14">
+        <v>0.261196048</v>
+      </c>
+      <c r="Z14">
+        <v>0.3587899847691182</v>
+      </c>
+      <c r="AA14">
+        <v>7.607295000000001</v>
+      </c>
+      <c r="AB14">
+        <v>0.04821241527016654</v>
+      </c>
+      <c r="AC14">
+        <v>24.21728060748791</v>
+      </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>46068.55143909722</v>
       </c>
@@ -1482,14 +1728,29 @@
       <c r="U15">
         <v>503.3414821853867</v>
       </c>
-      <c r="V15">
-        <v>0.5849827880852885</v>
-      </c>
-      <c r="W15" t="b">
+      <c r="V15" t="b">
         <v>1</v>
       </c>
+      <c r="X15">
+        <v>0.245983998</v>
+      </c>
+      <c r="Y15">
+        <v>0.261186182</v>
+      </c>
+      <c r="Z15">
+        <v>0.3587845438975892</v>
+      </c>
+      <c r="AA15">
+        <v>7.601092000000001</v>
+      </c>
+      <c r="AB15">
+        <v>0.04824936758146182</v>
+      </c>
+      <c r="AC15">
+        <v>24.28590819296054</v>
+      </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:29">
       <c r="A16" s="1">
         <v>46068.55155541666</v>
       </c>
@@ -1553,14 +1814,29 @@
       <c r="U16">
         <v>500.5240539871735</v>
       </c>
-      <c r="V16">
-        <v>1.424910470413982</v>
-      </c>
-      <c r="W16" t="b">
+      <c r="V16" t="b">
         <v>1</v>
       </c>
+      <c r="X16">
+        <v>0.245999558</v>
+      </c>
+      <c r="Y16">
+        <v>0.261181408</v>
+      </c>
+      <c r="Z16">
+        <v>0.3587917368349748</v>
+      </c>
+      <c r="AA16">
+        <v>7.590925000000006</v>
+      </c>
+      <c r="AB16">
+        <v>0.04831214388221578</v>
+      </c>
+      <c r="AC16">
+        <v>24.18139011273827</v>
+      </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:29">
       <c r="A17" s="1">
         <v>46068.55167115741</v>
       </c>
@@ -1624,14 +1900,29 @@
       <c r="U17">
         <v>500.4878910764361</v>
       </c>
-      <c r="V17">
-        <v>1.637182112924286</v>
-      </c>
-      <c r="W17" t="b">
+      <c r="V17" t="b">
         <v>1</v>
       </c>
+      <c r="X17">
+        <v>0.24600559</v>
+      </c>
+      <c r="Y17">
+        <v>0.261177906</v>
+      </c>
+      <c r="Z17">
+        <v>0.358793323368472</v>
+      </c>
+      <c r="AA17">
+        <v>7.586157999999998</v>
+      </c>
+      <c r="AB17">
+        <v>0.04834140666423159</v>
+      </c>
+      <c r="AC17">
+        <v>24.19428867304964</v>
+      </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:29">
       <c r="A18" s="1">
         <v>46068.55178747685</v>
       </c>
@@ -1695,14 +1986,29 @@
       <c r="U18">
         <v>503.5101158718723</v>
       </c>
-      <c r="V18">
-        <v>1.734537212510704</v>
-      </c>
-      <c r="W18" t="b">
+      <c r="V18" t="b">
         <v>1</v>
       </c>
+      <c r="X18">
+        <v>0.245988126</v>
+      </c>
+      <c r="Y18">
+        <v>0.261183636</v>
+      </c>
+      <c r="Z18">
+        <v>0.3587855206765908</v>
+      </c>
+      <c r="AA18">
+        <v>7.597755000000006</v>
+      </c>
+      <c r="AB18">
+        <v>0.04826977479749509</v>
+      </c>
+      <c r="AC18">
+        <v>24.30431990139593</v>
+      </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:29">
       <c r="A19" s="1">
         <v>46068.55190379629</v>
       </c>
@@ -1766,14 +2072,29 @@
       <c r="U19">
         <v>502.1690513595275</v>
       </c>
-      <c r="V19">
-        <v>1.514298332444036</v>
-      </c>
-      <c r="W19" t="b">
+      <c r="V19" t="b">
         <v>1</v>
       </c>
+      <c r="X19">
+        <v>0.245980188</v>
+      </c>
+      <c r="Y19">
+        <v>0.26118268</v>
+      </c>
+      <c r="Z19">
+        <v>0.3587793823793359</v>
+      </c>
+      <c r="AA19">
+        <v>7.601246000000003</v>
+      </c>
+      <c r="AB19">
+        <v>0.04824776775656341</v>
+      </c>
+      <c r="AC19">
+        <v>24.22853576452825</v>
+      </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:29">
       <c r="A20" s="1">
         <v>46068.55202011574</v>
       </c>
@@ -1837,14 +2158,29 @@
       <c r="U20">
         <v>500.7559902503633</v>
       </c>
-      <c r="V20">
-        <v>1.377219642586041</v>
-      </c>
-      <c r="W20" t="b">
+      <c r="V20" t="b">
         <v>1</v>
       </c>
+      <c r="X20">
+        <v>0.245981776</v>
+      </c>
+      <c r="Y20">
+        <v>0.261168676</v>
+      </c>
+      <c r="Z20">
+        <v>0.3587702767060102</v>
+      </c>
+      <c r="AA20">
+        <v>7.593450000000004</v>
+      </c>
+      <c r="AB20">
+        <v>0.04829400246343884</v>
+      </c>
+      <c r="AC20">
+        <v>24.1835110267328</v>
+      </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:29">
       <c r="A21" s="1">
         <v>46068.55213585648</v>
       </c>
@@ -1908,14 +2244,29 @@
       <c r="U21">
         <v>501.674806012278</v>
       </c>
-      <c r="V21">
-        <v>0.7170823483449144</v>
-      </c>
-      <c r="W21" t="b">
+      <c r="V21" t="b">
         <v>1</v>
       </c>
+      <c r="X21">
+        <v>0.245992254</v>
+      </c>
+      <c r="Y21">
+        <v>0.261165176</v>
+      </c>
+      <c r="Z21">
+        <v>0.3587749129790313</v>
+      </c>
+      <c r="AA21">
+        <v>7.586461</v>
+      </c>
+      <c r="AB21">
+        <v>0.04833718430456355</v>
+      </c>
+      <c r="AC21">
+        <v>24.24954755917165</v>
+      </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:29">
       <c r="A22" s="1">
         <v>46068.55225217593</v>
       </c>
@@ -1979,14 +2330,29 @@
       <c r="U22">
         <v>501.1921734999331</v>
       </c>
-      <c r="V22">
-        <v>0.4596035199884814</v>
-      </c>
-      <c r="W22" t="b">
+      <c r="V22" t="b">
         <v>1</v>
       </c>
+      <c r="X22">
+        <v>0.245981458</v>
+      </c>
+      <c r="Y22">
+        <v>0.26118268</v>
+      </c>
+      <c r="Z22">
+        <v>0.3587802530962206</v>
+      </c>
+      <c r="AA22">
+        <v>7.600611000000001</v>
+      </c>
+      <c r="AB22">
+        <v>0.04825173757880263</v>
+      </c>
+      <c r="AC22">
+        <v>24.18339323226849</v>
+      </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:29">
       <c r="A23" s="1">
         <v>46068.55236849537</v>
       </c>
@@ -2050,14 +2416,29 @@
       <c r="U23">
         <v>503.3849241761678</v>
       </c>
-      <c r="V23">
-        <v>1.152214809584727</v>
-      </c>
-      <c r="W23" t="b">
+      <c r="V23" t="b">
         <v>1</v>
       </c>
+      <c r="X23">
+        <v>0.245957008</v>
+      </c>
+      <c r="Y23">
+        <v>0.26117918</v>
+      </c>
+      <c r="Z23">
+        <v>0.3587609424809011</v>
+      </c>
+      <c r="AA23">
+        <v>7.611086</v>
+      </c>
+      <c r="AB23">
+        <v>0.04818570182653723</v>
+      </c>
+      <c r="AC23">
+        <v>24.25595586032687</v>
+      </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:29">
       <c r="A24" s="1">
         <v>46068.55248423611</v>
       </c>
@@ -2121,14 +2502,29 @@
       <c r="U24">
         <v>502.1015165103055</v>
       </c>
-      <c r="V24">
-        <v>1.101680192208474</v>
-      </c>
-      <c r="W24" t="b">
+      <c r="V24" t="b">
         <v>1</v>
       </c>
+      <c r="X24">
+        <v>0.24594621</v>
+      </c>
+      <c r="Y24">
+        <v>0.261171542</v>
+      </c>
+      <c r="Z24">
+        <v>0.3587479791776141</v>
+      </c>
+      <c r="AA24">
+        <v>7.612666000000004</v>
+      </c>
+      <c r="AB24">
+        <v>0.0481744659398629</v>
+      </c>
+      <c r="AC24">
+        <v>24.18847240547922</v>
+      </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:29">
       <c r="A25" s="1">
         <v>46068.55260055556</v>
       </c>
@@ -2192,14 +2588,29 @@
       <c r="U25">
         <v>504.9591352918457</v>
       </c>
-      <c r="V25">
-        <v>1.431273382581505</v>
-      </c>
-      <c r="W25" t="b">
+      <c r="V25" t="b">
         <v>1</v>
       </c>
+      <c r="X25">
+        <v>0.24595161</v>
+      </c>
+      <c r="Y25">
+        <v>0.261167086</v>
+      </c>
+      <c r="Z25">
+        <v>0.3587484373085456</v>
+      </c>
+      <c r="AA25">
+        <v>7.607737999999998</v>
+      </c>
+      <c r="AB25">
+        <v>0.04820438621519893</v>
+      </c>
+      <c r="AC25">
+        <v>24.34124518050102</v>
+      </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:29">
       <c r="A26" s="1">
         <v>46068.552716875</v>
       </c>
@@ -2263,14 +2674,29 @@
       <c r="U26">
         <v>503.4229780231545</v>
       </c>
-      <c r="V26">
-        <v>1.430152951301234</v>
-      </c>
-      <c r="W26" t="b">
+      <c r="V26" t="b">
         <v>1</v>
       </c>
+      <c r="X26">
+        <v>0.245958912</v>
+      </c>
+      <c r="Y26">
+        <v>0.261165812</v>
+      </c>
+      <c r="Z26">
+        <v>0.3587525160188331</v>
+      </c>
+      <c r="AA26">
+        <v>7.603450000000002</v>
+      </c>
+      <c r="AB26">
+        <v>0.04823092646065465</v>
+      </c>
+      <c r="AC26">
+        <v>24.28055663163853</v>
+      </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:29">
       <c r="A27" s="1">
         <v>46068.55283261574</v>
       </c>
@@ -2334,14 +2760,29 @@
       <c r="U27">
         <v>501.9678547907643</v>
       </c>
-      <c r="V27">
-        <v>1.495823174249626</v>
-      </c>
-      <c r="W27" t="b">
+      <c r="V27" t="b">
         <v>1</v>
       </c>
+      <c r="X27">
+        <v>0.245965264</v>
+      </c>
+      <c r="Y27">
+        <v>0.26117186</v>
+      </c>
+      <c r="Z27">
+        <v>0.3587612737607688</v>
+      </c>
+      <c r="AA27">
+        <v>7.603297999999995</v>
+      </c>
+      <c r="AB27">
+        <v>0.04823297601860433</v>
+      </c>
+      <c r="AC27">
+        <v>24.2114035022332</v>
+      </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:29">
       <c r="A28" s="1">
         <v>46068.55294893518</v>
       </c>
@@ -2405,14 +2846,29 @@
       <c r="U28">
         <v>504.9072168853726</v>
       </c>
-      <c r="V28">
-        <v>1.469705080663518</v>
-      </c>
-      <c r="W28" t="b">
+      <c r="V28" t="b">
         <v>1</v>
       </c>
+      <c r="X28">
+        <v>0.245936684</v>
+      </c>
+      <c r="Y28">
+        <v>0.261177588</v>
+      </c>
+      <c r="Z28">
+        <v>0.3587458501647282</v>
+      </c>
+      <c r="AA28">
+        <v>7.620452</v>
+      </c>
+      <c r="AB28">
+        <v>0.04812709356068827</v>
+      </c>
+      <c r="AC28">
+        <v>24.29971686650905</v>
+      </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:29">
       <c r="A29" s="1">
         <v>46068.55306525463</v>
       </c>
@@ -2476,14 +2932,29 @@
       <c r="U29">
         <v>504.5907186096722</v>
       </c>
-      <c r="V29">
-        <v>1.613455675161496</v>
-      </c>
-      <c r="W29" t="b">
+      <c r="V29" t="b">
         <v>1</v>
       </c>
+      <c r="X29">
+        <v>0.245933192</v>
+      </c>
+      <c r="Y29">
+        <v>0.26116995</v>
+      </c>
+      <c r="Z29">
+        <v>0.3587378955592946</v>
+      </c>
+      <c r="AA29">
+        <v>7.618378999999997</v>
+      </c>
+      <c r="AB29">
+        <v>0.04813860251782157</v>
+      </c>
+      <c r="AC29">
+        <v>24.29029203733296</v>
+      </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:29">
       <c r="A30" s="1">
         <v>46068.55318157408</v>
       </c>
@@ -2547,14 +3018,29 @@
       <c r="U30">
         <v>502.5421130242622</v>
       </c>
-      <c r="V30">
-        <v>1.283917980046556</v>
-      </c>
-      <c r="W30" t="b">
+      <c r="V30" t="b">
         <v>1</v>
       </c>
+      <c r="X30">
+        <v>0.24593732</v>
+      </c>
+      <c r="Y30">
+        <v>0.261172496</v>
+      </c>
+      <c r="Z30">
+        <v>0.3587425790670135</v>
+      </c>
+      <c r="AA30">
+        <v>7.617587999999998</v>
+      </c>
+      <c r="AB30">
+        <v>0.04814398688689828</v>
+      </c>
+      <c r="AC30">
+        <v>24.19438089955423</v>
+      </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:29">
       <c r="A31" s="1">
         <v>46068.55329789352</v>
       </c>
@@ -2618,14 +3104,29 @@
       <c r="U31">
         <v>503.5023265926084</v>
       </c>
-      <c r="V31">
-        <v>1.024970903994038</v>
-      </c>
-      <c r="W31" t="b">
+      <c r="V31" t="b">
         <v>1</v>
       </c>
+      <c r="X31">
+        <v>0.245937002</v>
+      </c>
+      <c r="Y31">
+        <v>0.261175042</v>
+      </c>
+      <c r="Z31">
+        <v>0.3587442146104237</v>
+      </c>
+      <c r="AA31">
+        <v>7.619019999999999</v>
+      </c>
+      <c r="AB31">
+        <v>0.04813553860211043</v>
+      </c>
+      <c r="AC31">
+        <v>24.23635567795091</v>
+      </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:29">
       <c r="A32" s="1">
         <v>46068.55341363426</v>
       </c>
@@ -2689,14 +3190,29 @@
       <c r="U32">
         <v>503.3952937942659</v>
       </c>
-      <c r="V32">
-        <v>0.5262102784773475</v>
-      </c>
-      <c r="W32" t="b">
+      <c r="V32" t="b">
         <v>1</v>
       </c>
+      <c r="X32">
+        <v>0.245944624</v>
+      </c>
+      <c r="Y32">
+        <v>0.261167404</v>
+      </c>
+      <c r="Z32">
+        <v>0.3587438793716216</v>
+      </c>
+      <c r="AA32">
+        <v>7.61139</v>
+      </c>
+      <c r="AB32">
+        <v>0.04818166719899053</v>
+      </c>
+      <c r="AC32">
+        <v>24.25442451513338</v>
+      </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:29">
       <c r="A33" s="1">
         <v>46068.553529375</v>
       </c>
@@ -2760,14 +3276,29 @@
       <c r="U33">
         <v>502.5704107242678</v>
       </c>
-      <c r="V33">
-        <v>0.5099600122795964</v>
-      </c>
-      <c r="W33" t="b">
+      <c r="V33" t="b">
         <v>1</v>
       </c>
+      <c r="X33">
+        <v>0.245949068</v>
+      </c>
+      <c r="Y33">
+        <v>0.261174724</v>
+      </c>
+      <c r="Z33">
+        <v>0.358752255054299</v>
+      </c>
+      <c r="AA33">
+        <v>7.612828</v>
+      </c>
+      <c r="AB33">
+        <v>0.04817403439926969</v>
+      </c>
+      <c r="AC33">
+        <v>24.21084425428598</v>
+      </c>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:29">
       <c r="A34" s="1">
         <v>46068.55364569445</v>
       </c>
@@ -2831,14 +3362,29 @@
       <c r="U34">
         <v>502.6603296903053</v>
       </c>
-      <c r="V34">
-        <v>0.4525280348081796</v>
-      </c>
-      <c r="W34" t="b">
+      <c r="V34" t="b">
         <v>1</v>
       </c>
+      <c r="X34">
+        <v>0.245951926</v>
+      </c>
+      <c r="Y34">
+        <v>0.261180452</v>
+      </c>
+      <c r="Z34">
+        <v>0.3587583844456235</v>
+      </c>
+      <c r="AA34">
+        <v>7.614263000000001</v>
+      </c>
+      <c r="AB34">
+        <v>0.04816613411347443</v>
+      </c>
+      <c r="AC34">
+        <v>24.21120485338652</v>
+      </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:29">
       <c r="A35" s="1">
         <v>46068.55376201389</v>
       </c>
@@ -2902,14 +3448,29 @@
       <c r="U35">
         <v>503.5035106405563</v>
       </c>
-      <c r="V35">
-        <v>0.5147353671366711</v>
-      </c>
-      <c r="W35" t="b">
+      <c r="V35" t="b">
         <v>1</v>
       </c>
+      <c r="X35">
+        <v>0.245962722</v>
+      </c>
+      <c r="Y35">
+        <v>0.26117727</v>
+      </c>
+      <c r="Z35">
+        <v>0.3587634694033134</v>
+      </c>
+      <c r="AA35">
+        <v>7.607273999999997</v>
+      </c>
+      <c r="AB35">
+        <v>0.04820913291264067</v>
+      </c>
+      <c r="AC35">
+        <v>24.27346766645177</v>
+      </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:29">
       <c r="A36" s="1">
         <v>46068.55387775463</v>
       </c>
@@ -2973,14 +3534,29 @@
       <c r="U36">
         <v>504.2254572639819</v>
       </c>
-      <c r="V36">
-        <v>0.7833459605876399</v>
-      </c>
-      <c r="W36" t="b">
+      <c r="V36" t="b">
         <v>1</v>
       </c>
+      <c r="X36">
+        <v>0.245964628</v>
+      </c>
+      <c r="Y36">
+        <v>0.261181726</v>
+      </c>
+      <c r="Z36">
+        <v>0.3587680200680065</v>
+      </c>
+      <c r="AA36">
+        <v>7.608548999999996</v>
+      </c>
+      <c r="AB36">
+        <v>0.04820198699708667</v>
+      </c>
+      <c r="AC36">
+        <v>24.30466893463853</v>
+      </c>
     </row>
-    <row r="37" spans="1:23">
+    <row r="37" spans="1:29">
       <c r="A37" s="1">
         <v>46068.55399407407</v>
       </c>
@@ -3044,14 +3620,29 @@
       <c r="U37">
         <v>502.4211549604685</v>
       </c>
-      <c r="V37">
-        <v>0.9081306392572684</v>
-      </c>
-      <c r="W37" t="b">
+      <c r="V37" t="b">
         <v>1</v>
       </c>
+      <c r="X37">
+        <v>0.24597225</v>
+      </c>
+      <c r="Y37">
+        <v>0.261172496</v>
+      </c>
+      <c r="Z37">
+        <v>0.3587665263607135</v>
+      </c>
+      <c r="AA37">
+        <v>7.600122999999996</v>
+      </c>
+      <c r="AB37">
+        <v>0.04825293581983842</v>
+      </c>
+      <c r="AC37">
+        <v>24.24329574483658</v>
+      </c>
     </row>
-    <row r="38" spans="1:23">
+    <row r="38" spans="1:29">
       <c r="A38" s="1">
         <v>46068.55411039352</v>
       </c>
@@ -3115,14 +3706,29 @@
       <c r="U38">
         <v>504.4607777589316</v>
       </c>
-      <c r="V38">
-        <v>1.115866158178313</v>
-      </c>
-      <c r="W38" t="b">
+      <c r="V38" t="b">
         <v>1</v>
       </c>
+      <c r="X38">
+        <v>0.245974472</v>
+      </c>
+      <c r="Y38">
+        <v>0.261168358</v>
+      </c>
+      <c r="Z38">
+        <v>0.3587650374494356</v>
+      </c>
+      <c r="AA38">
+        <v>7.596942999999996</v>
+      </c>
+      <c r="AB38">
+        <v>0.04827207493540311</v>
+      </c>
+      <c r="AC38">
+        <v>24.35136846595088</v>
+      </c>
     </row>
-    <row r="39" spans="1:23">
+    <row r="39" spans="1:29">
       <c r="A39" s="1">
         <v>46068.55422671296</v>
       </c>
@@ -3186,11 +3792,26 @@
       <c r="U39">
         <v>501.508152538568</v>
       </c>
-      <c r="V39">
-        <v>1.511711517581206</v>
-      </c>
-      <c r="W39" t="b">
+      <c r="V39" t="b">
         <v>1</v>
+      </c>
+      <c r="X39">
+        <v>0.245998604</v>
+      </c>
+      <c r="Y39">
+        <v>0.261178544</v>
+      </c>
+      <c r="Z39">
+        <v>0.3587889979025399</v>
+      </c>
+      <c r="AA39">
+        <v>7.589970000000001</v>
+      </c>
+      <c r="AB39">
+        <v>0.04831760923407445</v>
+      </c>
+      <c r="AC39">
+        <v>24.23167494206113</v>
       </c>
     </row>
   </sheetData>
